--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2021_magallanes_y_la_antartica_chilena.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2021_magallanes_y_la_antartica_chilena.xlsx
@@ -393,10 +393,10 @@
         <v>2021</v>
       </c>
       <c r="C2">
+        <v>25.01107900661195</v>
+      </c>
+      <c r="D2">
         <v>31.68064098700654</v>
-      </c>
-      <c r="D2">
-        <v>25.01107900661195</v>
       </c>
       <c r="E2">
         <v>3.156501790510295</v>
@@ -454,16 +454,16 @@
         <v>2018</v>
       </c>
       <c r="B2">
+        <v>30.96463348286845</v>
+      </c>
+      <c r="C2">
+        <v>29.70059769434318</v>
+      </c>
+      <c r="D2">
         <v>26.09399171923384</v>
       </c>
-      <c r="C2">
+      <c r="E2">
         <v>27.4254732517903</v>
-      </c>
-      <c r="D2">
-        <v>30.96463348286845</v>
-      </c>
-      <c r="E2">
-        <v>29.70059769434318</v>
       </c>
       <c r="F2">
         <v>3.832299828864059</v>
@@ -477,16 +477,16 @@
         <v>2019</v>
       </c>
       <c r="B3">
+        <v>30.71165626375393</v>
+      </c>
+      <c r="C3">
+        <v>29.28342029465625</v>
+      </c>
+      <c r="D3">
         <v>26.98100995207131</v>
       </c>
-      <c r="C3">
+      <c r="E3">
         <v>28.41472729113179</v>
-      </c>
-      <c r="D3">
-        <v>30.71165626375393</v>
-      </c>
-      <c r="E3">
-        <v>29.28342029465625</v>
       </c>
       <c r="F3">
         <v>3.706310481988576</v>
@@ -500,16 +500,16 @@
         <v>2020</v>
       </c>
       <c r="B4">
+        <v>29.29313247284859</v>
+      </c>
+      <c r="C4">
+        <v>27.75197884386445</v>
+      </c>
+      <c r="D4">
         <v>28.337590420799</v>
       </c>
-      <c r="C4">
+      <c r="E4">
         <v>29.85486963712865</v>
-      </c>
-      <c r="D4">
-        <v>29.29313247284859</v>
-      </c>
-      <c r="E4">
-        <v>27.75197884386445</v>
       </c>
       <c r="F4">
         <v>3.528881549738357</v>
@@ -523,16 +523,16 @@
         <v>2021</v>
       </c>
       <c r="B5">
+        <v>28.1958714984216</v>
+      </c>
+      <c r="C5">
+        <v>25.01107900661195</v>
+      </c>
+      <c r="D5">
         <v>30.43836759383663</v>
       </c>
-      <c r="C5">
+      <c r="E5">
         <v>31.68064098700654</v>
-      </c>
-      <c r="D5">
-        <v>28.1958714984216</v>
-      </c>
-      <c r="E5">
-        <v>25.01107900661195</v>
       </c>
       <c r="F5">
         <v>3.285327299229039</v>
@@ -546,16 +546,16 @@
         <v>2022</v>
       </c>
       <c r="B6">
+        <v>27.7896259030398</v>
+      </c>
+      <c r="C6">
+        <v>25.6707411153589</v>
+      </c>
+      <c r="D6">
         <v>30.85942857605788</v>
       </c>
-      <c r="C6">
+      <c r="E6">
         <v>31.62555073631517</v>
-      </c>
-      <c r="D6">
-        <v>27.7896259030398</v>
-      </c>
-      <c r="E6">
-        <v>25.6707411153589</v>
       </c>
       <c r="F6">
         <v>3.240500703165465</v>
@@ -569,16 +569,16 @@
         <v>2023</v>
       </c>
       <c r="B7">
+        <v>27.41672147958797</v>
+      </c>
+      <c r="C7">
+        <v>25.05299507658643</v>
+      </c>
+      <c r="D7">
         <v>32.03512600577511</v>
       </c>
-      <c r="C7">
+      <c r="E7">
         <v>32.60308397155361</v>
-      </c>
-      <c r="D7">
-        <v>27.41672147958797</v>
-      </c>
-      <c r="E7">
-        <v>25.05299507658643</v>
       </c>
       <c r="F7">
         <v>3.121573487239369</v>
@@ -592,16 +592,16 @@
         <v>2024</v>
       </c>
       <c r="B8">
+        <v>26.56912786797274</v>
+      </c>
+      <c r="C8">
+        <v>24.37632662180859</v>
+      </c>
+      <c r="D8">
         <v>33.29424476531351</v>
       </c>
-      <c r="C8">
+      <c r="E8">
         <v>33.97268985193397</v>
-      </c>
-      <c r="D8">
-        <v>26.56912786797274</v>
-      </c>
-      <c r="E8">
-        <v>24.37632662180859</v>
       </c>
       <c r="F8">
         <v>3.003522101338716</v>
@@ -649,10 +649,10 @@
         </is>
       </c>
       <c r="B2">
+        <v>24.89952217210735</v>
+      </c>
+      <c r="C2">
         <v>32.38400392979949</v>
-      </c>
-      <c r="C2">
-        <v>24.89952217210735</v>
       </c>
       <c r="D2">
         <v>3.087944289309477</v>
@@ -665,10 +665,10 @@
         </is>
       </c>
       <c r="B3">
+        <v>24.41349820871374</v>
+      </c>
+      <c r="C3">
         <v>30.39986131977349</v>
-      </c>
-      <c r="C3">
-        <v>24.41349820871374</v>
       </c>
       <c r="D3">
         <v>3.289488690363049</v>
@@ -681,10 +681,10 @@
         </is>
       </c>
       <c r="B4">
+        <v>32.98804780876494</v>
+      </c>
+      <c r="C4">
         <v>12.43027888446215</v>
-      </c>
-      <c r="C4">
-        <v>32.98804780876494</v>
       </c>
       <c r="D4">
         <v>8.044871794871796</v>
@@ -697,10 +697,10 @@
         </is>
       </c>
       <c r="B5">
+        <v>27.21073939910505</v>
+      </c>
+      <c r="C5">
         <v>28.12699765608353</v>
-      </c>
-      <c r="C5">
-        <v>27.21073939910505</v>
       </c>
       <c r="D5">
         <v>3.55530303030303</v>

--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2021_magallanes_y_la_antartica_chilena.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2021_magallanes_y_la_antartica_chilena.xlsx
@@ -1,48 +1,151 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="resumen" sheetId="1" r:id="rId1"/>
-    <sheet name="serie_anual" sheetId="2" r:id="rId2"/>
-    <sheet name="provincias" sheetId="3" r:id="rId3"/>
+    <sheet name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Serie_anual" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Provincias" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Provincias'!$A$1:$D$5</definedName>
+  </definedNames>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+  <si>
+    <t xml:space="preserve">Territorio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">depmen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">depmay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">apoyo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magallanes y la Antartica Chilena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fecha de creación</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-27 20:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fuente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIT - MDSF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imagen asociada</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Indicador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unidad territorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Año</t>
+  </si>
+  <si>
+    <t xml:space="preserve">year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">depmen_nac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">depmen_reg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">depmay_nac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">depmay_reg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">apoyo_nac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">apoyo_reg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Provincia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magallanes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Última Esperanza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antártica Chilena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tierra del Fuego</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
       <b/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00135A"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -50,21 +153,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
 </file>
 
@@ -114,10 +233,6 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -143,15 +258,12 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -177,6 +289,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -352,361 +465,418 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="35.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="10.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="10.71" hidden="0" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Territorio</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Anio</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>depmen</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>depmay</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>apoyo</t>
-        </is>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Magallanes y la Antártica Chilena</t>
-        </is>
-      </c>
-      <c r="B2">
+      <c r="A2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="C2">
-        <v>25.01107900661195</v>
-      </c>
-      <c r="D2">
-        <v>31.68064098700654</v>
-      </c>
-      <c r="E2">
-        <v>3.156501790510295</v>
+      <c r="C2" s="2" t="n">
+        <v>25.01</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>31.68</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>3.16</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="24.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="60.71" hidden="0" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>year</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>depmen_nac</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>depmen_reg</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>depmay_nac</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>depmay_reg</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>apoyo_nac</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>apoyo_reg</t>
-        </is>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>2018</v>
-      </c>
-      <c r="B2">
-        <v>30.96463348286845</v>
-      </c>
-      <c r="C2">
-        <v>29.70059769434318</v>
-      </c>
-      <c r="D2">
-        <v>26.09399171923384</v>
-      </c>
-      <c r="E2">
-        <v>27.4254732517903</v>
-      </c>
-      <c r="F2">
-        <v>3.832299828864059</v>
-      </c>
-      <c r="G2">
-        <v>3.646245192632076</v>
+      <c r="A2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2019</v>
-      </c>
-      <c r="B3">
-        <v>30.71165626375393</v>
-      </c>
-      <c r="C3">
-        <v>29.28342029465625</v>
-      </c>
-      <c r="D3">
-        <v>26.98100995207131</v>
-      </c>
-      <c r="E3">
-        <v>28.41472729113179</v>
-      </c>
-      <c r="F3">
-        <v>3.706310481988576</v>
-      </c>
-      <c r="G3">
-        <v>3.519301768249239</v>
+      <c r="A3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>2020</v>
-      </c>
-      <c r="B4">
-        <v>29.29313247284859</v>
-      </c>
-      <c r="C4">
-        <v>27.75197884386445</v>
-      </c>
-      <c r="D4">
-        <v>28.337590420799</v>
-      </c>
-      <c r="E4">
-        <v>29.85486963712865</v>
-      </c>
-      <c r="F4">
-        <v>3.528881549738357</v>
-      </c>
-      <c r="G4">
-        <v>3.349537318884695</v>
+      <c r="A4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>2021</v>
-      </c>
-      <c r="B5">
-        <v>28.1958714984216</v>
-      </c>
-      <c r="C5">
-        <v>25.01107900661195</v>
-      </c>
-      <c r="D5">
-        <v>30.43836759383663</v>
-      </c>
-      <c r="E5">
-        <v>31.68064098700654</v>
-      </c>
-      <c r="F5">
-        <v>3.285327299229039</v>
-      </c>
-      <c r="G5">
-        <v>3.156501790510295</v>
+      <c r="A5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>2022</v>
-      </c>
-      <c r="B6">
-        <v>27.7896259030398</v>
-      </c>
-      <c r="C6">
-        <v>25.6707411153589</v>
-      </c>
-      <c r="D6">
-        <v>30.85942857605788</v>
-      </c>
-      <c r="E6">
-        <v>31.62555073631517</v>
-      </c>
-      <c r="F6">
-        <v>3.240500703165465</v>
-      </c>
-      <c r="G6">
-        <v>3.162000271039436</v>
+      <c r="A6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>2023</v>
-      </c>
-      <c r="B7">
-        <v>27.41672147958797</v>
-      </c>
-      <c r="C7">
-        <v>25.05299507658643</v>
-      </c>
-      <c r="D7">
-        <v>32.03512600577511</v>
-      </c>
-      <c r="E7">
-        <v>32.60308397155361</v>
-      </c>
-      <c r="F7">
-        <v>3.121573487239369</v>
-      </c>
-      <c r="G7">
-        <v>3.067194504889495</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8">
-        <v>2024</v>
-      </c>
-      <c r="B8">
-        <v>26.56912786797274</v>
-      </c>
-      <c r="C8">
-        <v>24.37632662180859</v>
-      </c>
-      <c r="D8">
-        <v>33.29424476531351</v>
-      </c>
-      <c r="E8">
-        <v>33.97268985193397</v>
-      </c>
-      <c r="F8">
-        <v>3.003522101338716</v>
-      </c>
-      <c r="G8">
-        <v>2.943540839298814</v>
+      <c r="A7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="10.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="12.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="12.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="12.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="11.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="11.71" hidden="0" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Provincia</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>depmen</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>depmay</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>apoyo</t>
-        </is>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Magallanes</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>24.89952217210735</v>
-      </c>
-      <c r="C2">
-        <v>32.38400392979949</v>
-      </c>
-      <c r="D2">
-        <v>3.087944289309477</v>
+      <c r="A2" s="2" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>30.96</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>26.09</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>27.43</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>3.65</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Última Esperanza</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>24.41349820871374</v>
-      </c>
-      <c r="C3">
-        <v>30.39986131977349</v>
-      </c>
-      <c r="D3">
-        <v>3.289488690363049</v>
+      <c r="A3" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>30.71</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>29.28</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>26.98</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>28.41</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>3.52</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Antártica Chilena</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>32.98804780876494</v>
-      </c>
-      <c r="C4">
-        <v>12.43027888446215</v>
-      </c>
-      <c r="D4">
-        <v>8.044871794871796</v>
+      <c r="A4" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>29.29</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>27.75</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>28.34</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>29.85</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>3.35</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Tierra del Fuego</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>27.21073939910505</v>
-      </c>
-      <c r="C5">
-        <v>28.12699765608353</v>
-      </c>
-      <c r="D5">
-        <v>3.55530303030303</v>
+      <c r="A5" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>25.01</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>30.44</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>31.68</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>3.16</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>27.79</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>25.67</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>30.86</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>3.16</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>27.42</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>25.05</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>32.04</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>3.07</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>26.57</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>24.38</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>33.29</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>33.97</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>2.94</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="19.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="10.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>3.09</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>24.41</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>3.29</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>32.99</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>8.04</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>27.21</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>28.13</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>3.56</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2021_magallanes_y_la_antartica_chilena.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2021_magallanes_y_la_antartica_chilena.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t xml:space="preserve">Territorio</t>
   </si>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 20:59</t>
+    <t xml:space="preserve">2026-07-30 18:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -59,16 +59,25 @@
     <t xml:space="preserve">Imagen asociada</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">plot_regional_d_otrasrel_a_2021_magallanes_y_la_antartica_chilena.png</t>
   </si>
   <si>
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
+    <t xml:space="preserve">Otras relaciones demograficas</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
+    <t xml:space="preserve">Region de Magallanes y la Antartica Chilena</t>
+  </si>
+  <si>
     <t xml:space="preserve">Año</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021</t>
   </si>
   <si>
     <t xml:space="preserve">year</t>
@@ -563,23 +572,23 @@
         <v>14</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -604,25 +613,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2">
@@ -806,7 +815,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
@@ -820,7 +829,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>24.9</v>
@@ -834,7 +843,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>24.41</v>
@@ -848,7 +857,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>32.99</v>
@@ -862,7 +871,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>27.21</v>

--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2021_magallanes_y_la_antartica_chilena.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2021_magallanes_y_la_antartica_chilena.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 18:26</t>
+    <t xml:space="preserve">2026-08-07 07:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2021_magallanes_y_la_antartica_chilena.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2021_magallanes_y_la_antartica_chilena.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-07 07:04</t>
+    <t xml:space="preserve">2026-08-17 16:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2021_magallanes_y_la_antartica_chilena.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2021_magallanes_y_la_antartica_chilena.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-17 16:32</t>
+    <t xml:space="preserve">2026-08-19 13:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2021_magallanes_y_la_antartica_chilena.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2021_magallanes_y_la_antartica_chilena.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 13:01</t>
+    <t xml:space="preserve">2026-08-28 11:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2021_magallanes_y_la_antartica_chilena.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2021_magallanes_y_la_antartica_chilena.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 11:01</t>
+    <t xml:space="preserve">2026-09-04 20:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2021_magallanes_y_la_antartica_chilena.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2021_magallanes_y_la_antartica_chilena.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-04 20:36</t>
+    <t xml:space="preserve">2026-09-06 17:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
